--- a/inst/templates/ModelParameters.xlsx
+++ b/inst/templates/ModelParameters.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ztcok\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub repositories\ESQlabs\esqlabsR\inst\extdata\examples\TestProject\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123D1162-2BA0-4B5A-AD10-0B32C04029E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23F2110-7F6E-4E34-A95E-F3FC5A35A589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" tabRatio="976" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="5" r:id="rId1"/>
+    <sheet name="Global" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet, with comma" sheetId="8" r:id="rId2"/>
+    <sheet name="MissingParam" sheetId="7" r:id="rId3"/>
+    <sheet name="Aciclovir" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="11">
   <si>
     <t>Container Path</t>
   </si>
@@ -48,10 +51,25 @@
     <t>Units</t>
   </si>
   <si>
+    <t>Aciclovir</t>
+  </si>
+  <si>
+    <t>Lipophilicity</t>
+  </si>
+  <si>
+    <t>Log Units</t>
+  </si>
+  <si>
     <t>EHC continuous fraction</t>
   </si>
   <si>
     <t>Organism|Liver</t>
+  </si>
+  <si>
+    <t>foo</t>
+  </si>
+  <si>
+    <t>bar</t>
   </si>
 </sst>
 </file>
@@ -404,10 +422,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -417,6 +435,120 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC16AB98-5CE4-407B-B818-A3F5E3A90958}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="71.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB1D1D3-9309-4BAC-A19A-8F08944F068E}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003F998E-5869-417D-A696-38B00449383B}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
